--- a/artfynd/A 20205-2025 artfynd.xlsx
+++ b/artfynd/A 20205-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129297974</v>
       </c>
       <c r="B2" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129297976</v>
       </c>
       <c r="B4" t="n">
-        <v>91547</v>
+        <v>91554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129297975</v>
       </c>
       <c r="B7" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 20205-2025 artfynd.xlsx
+++ b/artfynd/A 20205-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129297974</v>
       </c>
       <c r="B2" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129297973</v>
       </c>
       <c r="B3" t="n">
-        <v>80048</v>
+        <v>80050</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129297976</v>
       </c>
       <c r="B4" t="n">
-        <v>91554</v>
+        <v>91556</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129297971</v>
       </c>
       <c r="B5" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129297972</v>
       </c>
       <c r="B6" t="n">
-        <v>80104</v>
+        <v>80106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129297975</v>
       </c>
       <c r="B7" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 20205-2025 artfynd.xlsx
+++ b/artfynd/A 20205-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129297974</v>
       </c>
       <c r="B2" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129297976</v>
       </c>
       <c r="B4" t="n">
-        <v>91556</v>
+        <v>91554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129297975</v>
       </c>
       <c r="B7" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 20205-2025 artfynd.xlsx
+++ b/artfynd/A 20205-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129297974</v>
       </c>
       <c r="B2" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20205-2025 artfynd.xlsx
+++ b/artfynd/A 20205-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129297974</v>
       </c>
       <c r="B2" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129297973</v>
       </c>
       <c r="B3" t="n">
-        <v>80050</v>
+        <v>80052</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129297976</v>
       </c>
       <c r="B4" t="n">
-        <v>91554</v>
+        <v>91557</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129297971</v>
       </c>
       <c r="B5" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129297972</v>
       </c>
       <c r="B6" t="n">
-        <v>80106</v>
+        <v>80108</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129297975</v>
       </c>
       <c r="B7" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 20205-2025 artfynd.xlsx
+++ b/artfynd/A 20205-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129297974</v>
       </c>
       <c r="B2" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129297973</v>
       </c>
       <c r="B3" t="n">
-        <v>80052</v>
+        <v>80053</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129297976</v>
       </c>
       <c r="B4" t="n">
-        <v>91557</v>
+        <v>91559</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129297971</v>
       </c>
       <c r="B5" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129297972</v>
       </c>
       <c r="B6" t="n">
-        <v>80108</v>
+        <v>80109</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129297975</v>
       </c>
       <c r="B7" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 20205-2025 artfynd.xlsx
+++ b/artfynd/A 20205-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129297974</v>
       </c>
       <c r="B2" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129297976</v>
       </c>
       <c r="B4" t="n">
-        <v>91559</v>
+        <v>91563</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129297975</v>
       </c>
       <c r="B7" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 20205-2025 artfynd.xlsx
+++ b/artfynd/A 20205-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129297974</v>
       </c>
       <c r="B2" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129297976</v>
       </c>
       <c r="B4" t="n">
-        <v>91563</v>
+        <v>91564</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129297975</v>
       </c>
       <c r="B7" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 20205-2025 artfynd.xlsx
+++ b/artfynd/A 20205-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129297974</v>
       </c>
       <c r="B2" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129297976</v>
       </c>
       <c r="B4" t="n">
-        <v>91564</v>
+        <v>91567</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129297975</v>
       </c>
       <c r="B7" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 20205-2025 artfynd.xlsx
+++ b/artfynd/A 20205-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129297974</v>
       </c>
       <c r="B2" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129297973</v>
       </c>
       <c r="B3" t="n">
-        <v>80053</v>
+        <v>80079</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129297976</v>
       </c>
       <c r="B4" t="n">
-        <v>91567</v>
+        <v>91595</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129297971</v>
       </c>
       <c r="B5" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129297972</v>
       </c>
       <c r="B6" t="n">
-        <v>80109</v>
+        <v>80135</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129297975</v>
       </c>
       <c r="B7" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 20205-2025 artfynd.xlsx
+++ b/artfynd/A 20205-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129297974</v>
       </c>
       <c r="B2" t="n">
-        <v>91879</v>
+        <v>91885</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129297973</v>
       </c>
       <c r="B3" t="n">
-        <v>80079</v>
+        <v>80084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129297976</v>
       </c>
       <c r="B4" t="n">
-        <v>91595</v>
+        <v>91601</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129297971</v>
       </c>
       <c r="B5" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129297972</v>
       </c>
       <c r="B6" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129297975</v>
       </c>
       <c r="B7" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 20205-2025 artfynd.xlsx
+++ b/artfynd/A 20205-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129297974</v>
       </c>
       <c r="B2" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129297973</v>
       </c>
       <c r="B3" t="n">
-        <v>80084</v>
+        <v>80085</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129297976</v>
       </c>
       <c r="B4" t="n">
-        <v>91601</v>
+        <v>91602</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129297971</v>
       </c>
       <c r="B5" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129297972</v>
       </c>
       <c r="B6" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129297975</v>
       </c>
       <c r="B7" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 20205-2025 artfynd.xlsx
+++ b/artfynd/A 20205-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129297974</v>
       </c>
       <c r="B2" t="n">
-        <v>91886</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129297973</v>
+        <v>129297975</v>
       </c>
       <c r="B3" t="n">
-        <v>80085</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>610404</v>
+        <v>610445</v>
       </c>
       <c r="R3" t="n">
-        <v>7002558</v>
+        <v>7002547</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,11 +872,11 @@
         <v>129297976</v>
       </c>
       <c r="B4" t="n">
-        <v>91602</v>
+        <v>91923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129297971</v>
+        <v>129297973</v>
       </c>
       <c r="B5" t="n">
-        <v>80181</v>
+        <v>80336</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>610510</v>
+        <v>610404</v>
       </c>
       <c r="R5" t="n">
-        <v>7002715</v>
+        <v>7002558</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129297972</v>
+        <v>129297971</v>
       </c>
       <c r="B6" t="n">
-        <v>80141</v>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>610505</v>
+        <v>610510</v>
       </c>
       <c r="R6" t="n">
-        <v>7002710</v>
+        <v>7002715</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129297975</v>
+        <v>129297972</v>
       </c>
       <c r="B7" t="n">
-        <v>91588</v>
+        <v>80392</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>610445</v>
+        <v>610505</v>
       </c>
       <c r="R7" t="n">
-        <v>7002547</v>
+        <v>7002710</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 20205-2025 artfynd.xlsx
+++ b/artfynd/A 20205-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129297974</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129297975</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129297976</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129297973</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129297971</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,8 +1284,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129297972</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>